--- a/naver-place-crawler/results_derma/청라_피부과.xlsx
+++ b/naver-place-crawler/results_derma/청라_피부과.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,44 +564,44 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>서울더본피부과의원</t>
+          <t>이너스피부과의원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>darguji@naver.com</t>
+          <t>laugh5ne@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>032-710-0075</t>
+          <t>032-262-1777</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 9-4</t>
+          <t>인천광역시 서구 서곶로 281 자혜빌딩 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://seoulderborn.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>823</v>
+        <v>361</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>832</v>
+        <v>361</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1062309841</t>
+          <t>36428624</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1062309841</t>
+          <t>https://m.place.naver.com/place/36428624</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,38 +658,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>킵슨의원</t>
+          <t>클린업피부과의원 인천청라</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>keepsonmedical@naver.com</t>
+          <t>cleanup-cr@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>jhjang@carecrm.co.kr</t>
+          <t>promotion@cunetwork.co.kr</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>032-567-5337</t>
+          <t>0507-1421-7590</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 93 루비타워 3층</t>
+          <t>인천광역시 서구 중봉대로 610 마루힐프라자 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/332287/items/3362791</t>
+          <t>http://www.upskincr.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>443</v>
+        <v>715</v>
       </c>
       <c r="Q3" t="n">
-        <v>98</v>
+        <v>562</v>
       </c>
       <c r="R3" t="n">
-        <v>541</v>
+        <v>1277</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>813673396</t>
+          <t>839147805</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/813673396</t>
+          <t>https://m.place.naver.com/place/839147805</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -756,24 +756,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이너스피부과의원</t>
+          <t>청라의원</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>laugh5ne@naver.com</t>
+          <t>cnvclinic@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>032-262-1777</t>
+          <t>032-208-7711</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 281 자혜빌딩 3층</t>
+          <t>인천광역시 서구 청라에메랄드로 78 딜라이트타워1차 305호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>361</v>
+        <v>100</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>361</v>
+        <v>102</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>36428624</t>
+          <t>21795997</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428624</t>
+          <t>https://m.place.naver.com/place/21795997</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -850,35 +850,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>연세뉴피부과의원</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>고운의원</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>thegounclinic@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>032-562-0712</t>
+          <t>0507-1496-2806</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 4층 405호</t>
+          <t>인천광역시 서구 거북로 98 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://ysnewderma.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -899,17 +903,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>490</v>
+        <v>74</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>502</v>
+        <v>78</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1657698874</t>
+          <t>13240170</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657698874</t>
+          <t>https://m.place.naver.com/place/13240170</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>청라의원</t>
+          <t>현대아이비의원</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cnvclinic@naver.com</t>
+          <t>hdib0754@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>032-208-7711</t>
+          <t>0507-1405-0754</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 78 딜라이트타워1차 305호</t>
+          <t>인천광역시 서구 탁옥로 45 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.ibclinic.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,12 +976,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>100</v>
+        <v>384</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="R6" t="n">
-        <v>102</v>
+        <v>458</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>21795997</t>
+          <t>32839994</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21795997</t>
+          <t>https://m.place.naver.com/place/32839994</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1034,38 +1038,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>클린업피부과의원 인천청라</t>
+          <t>다시봄날의원 가정청라점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cleanup-cr@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>promotion@cunetwork.co.kr</t>
-        </is>
-      </c>
+          <t>springdayclinic12@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1421-7590</t>
+          <t>032-710-7525</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 610 마루힐프라자 4층</t>
+          <t>인천광역시 서구 염곡로464번길 7 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.upskincr.co.kr/</t>
+          <t>https://igc.springdayclinic.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1086,7 +1086,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>715</v>
+        <v>282</v>
       </c>
       <c r="Q7" t="n">
-        <v>562</v>
+        <v>12</v>
       </c>
       <c r="R7" t="n">
-        <v>1277</v>
+        <v>294</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>839147805</t>
+          <t>1545423432</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/839147805</t>
+          <t>https://m.place.naver.com/place/1545423432</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1132,25 +1132,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>다시봄날의원 가정청라점</t>
+          <t>연세뉴피부과의원</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>032-710-7525</t>
+          <t>032-562-0712</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 7 4층</t>
+          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 4층 405호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://igc.springdayclinic.com/</t>
+          <t>https://ysnewderma.co.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,7 +1176,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>279</v>
+        <v>491</v>
       </c>
       <c r="Q8" t="n">
         <v>12</v>
       </c>
       <c r="R8" t="n">
-        <v>291</v>
+        <v>503</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1545423432</t>
+          <t>1657698874</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1545423432</t>
+          <t>https://m.place.naver.com/place/1657698874</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1222,39 +1222,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>청라브이의원</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>cnvclinic@naver.com</t>
-        </is>
-      </c>
+          <t>미라클비뇨기과의원</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>032-567-8258</t>
+          <t>032-572-8275</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 7-11 퍼스트타워 2층</t>
+          <t>인천광역시 서구 가정로 363 3층 미라클</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/mr4enztn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1270,22 +1266,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>913</v>
+        <v>484</v>
       </c>
       <c r="Q9" t="n">
-        <v>568</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1481</v>
+        <v>485</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1958745925</t>
+          <t>13137484</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958745925</t>
+          <t>https://m.place.naver.com/place/13137484</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1316,44 +1312,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휴먼피부과의원 청라점</t>
+          <t>로지의원</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>human___ch@naver.com</t>
+          <t>srh0606@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>032-283-3335</t>
+          <t>032-569-6515</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 594 청라비전프라자 4층</t>
+          <t>인천광역시 서구 봉오재3로 90 한일골드타워 201호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.humanic.co.kr</t>
+          <t>http://www.rosyclinic.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2921</v>
+        <v>613</v>
       </c>
       <c r="Q10" t="n">
-        <v>1085</v>
+        <v>501</v>
       </c>
       <c r="R10" t="n">
-        <v>4006</v>
+        <v>1114</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1835204658</t>
+          <t>1915321940</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835204658</t>
+          <t>https://m.place.naver.com/place/1915321940</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,34 +1406,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>미엘피부과의원</t>
+          <t>더예쁨의원</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mgsj010@naver.com</t>
+          <t>artificial6244@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>032-572-7111</t>
+          <t>0507-1314-6110</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 375 403, 404호 금강아미움</t>
+          <t>인천광역시 서구 중봉대로 602 청라여성병원 1층 101호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://ic.mielskin.co.kr/</t>
+          <t>http://theyeppeum.co.kr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1458,22 +1454,22 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1521</v>
+        <v>390</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>270</v>
       </c>
       <c r="R11" t="n">
-        <v>1524</v>
+        <v>660</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1405806250</t>
+          <t>1315061387</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1405806250</t>
+          <t>https://m.place.naver.com/place/1315061387</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1504,29 +1500,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>더예쁨의원</t>
+          <t>닥터에버스의원 청라</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>artificial6244@naver.com</t>
+          <t>drevers777@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1314-6110</t>
+          <t>0507-1411-8830</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 602 청라여성병원 1층 101호</t>
+          <t>인천광역시 서구 가정로 451 벨라미센텀시티 10층 1036호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://theyeppeum.co.kr</t>
+          <t>https://evers7.co.kr/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1536,12 +1532,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1561,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>390</v>
+        <v>1300</v>
       </c>
       <c r="Q12" t="n">
-        <v>255</v>
+        <v>1301</v>
       </c>
       <c r="R12" t="n">
-        <v>645</v>
+        <v>2601</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1315061387</t>
+          <t>1008759002</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315061387</t>
+          <t>https://m.place.naver.com/place/1008759002</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1598,44 +1594,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>더율피부과의원</t>
+          <t>미엘피부과의원</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>theyulderma@naver.com</t>
+          <t>mielskin@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>032-225-2223</t>
+          <t>032-572-7111</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 588 406호, 407호</t>
+          <t>인천광역시 서구 가정로 375 403, 404호 금강아미움</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://the-yul.co.kr/</t>
+          <t>http://ic.mielskin.co.kr/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1646,7 +1642,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1655,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>386</v>
+        <v>1518</v>
       </c>
       <c r="Q13" t="n">
-        <v>196</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>582</v>
+        <v>1521</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1246412735</t>
+          <t>1405806250</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1246412735</t>
+          <t>https://m.place.naver.com/place/1405806250</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1692,40 +1688,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>고운의원</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>파크뷰의원 청라점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>parkview3300@naver.com</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1496-2806</t>
+          <t>032-565-3300</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 서구 거북로 98 3층</t>
+          <t>인천광역시 서구 청라라임로 65 라임타워 파크뷰의원</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://parkviewcl.com/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1736,22 +1736,22 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>74</v>
+        <v>1051</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>2417</v>
       </c>
       <c r="R14" t="n">
-        <v>78</v>
+        <v>3468</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,17 +1760,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>13240170</t>
+          <t>34716369</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240170</t>
+          <t>https://m.place.naver.com/place/34716369</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1782,29 +1782,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>데일리의원</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>daily_clinic@naver.com</t>
-        </is>
-      </c>
+          <t>서울더본피부과의원</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>032-567-5430</t>
+          <t>032-710-0075</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 서구 솔빛로 20 도영프라자 2층</t>
+          <t>인천광역시 서구 중봉대로586번길 9-4</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://dailyclinic.qshop.ai/</t>
+          <t>http://seoulderborn.com</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1819,7 +1815,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1835,17 +1831,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>362</v>
+        <v>824</v>
       </c>
       <c r="Q15" t="n">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>474</v>
+        <v>833</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,17 +1850,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1443622999</t>
+          <t>1062309841</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1443622999</t>
+          <t>https://m.place.naver.com/place/1062309841</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1876,29 +1872,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>파크뷰의원 청라점</t>
+          <t>데일리의원</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>parkview3300@naver.com</t>
+          <t>daily_clinic@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>032-565-3300</t>
+          <t>032-567-5430</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 65 라임타워 파크뷰의원</t>
+          <t>인천광역시 서구 솔빛로 20 도영프라자 2층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://parkviewcl.com/</t>
+          <t>https://dailyclinic.qshop.ai/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1913,7 +1909,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1924,22 +1920,22 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1049</v>
+        <v>363</v>
       </c>
       <c r="Q16" t="n">
-        <v>2408</v>
+        <v>112</v>
       </c>
       <c r="R16" t="n">
-        <v>3457</v>
+        <v>475</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>34716369</t>
+          <t>1443622999</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34716369</t>
+          <t>https://m.place.naver.com/place/1443622999</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1970,34 +1966,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>로지의원</t>
+          <t>킵슨의원</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>srh0606@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>keepsonmedical@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>jhjang@carecrm.co.kr</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>032-569-6515</t>
+          <t>032-567-5337</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 90 한일골드타워 201호</t>
+          <t>인천광역시 서구 청라루비로 93 루비타워 3층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://www.rosyclinic.co.kr/</t>
+          <t>https://booking.naver.com/booking/13/bizes/332287/items/3362791</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2018,7 +2018,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2027,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>614</v>
+        <v>444</v>
       </c>
       <c r="Q17" t="n">
-        <v>496</v>
+        <v>98</v>
       </c>
       <c r="R17" t="n">
-        <v>1110</v>
+        <v>542</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1915321940</t>
+          <t>813673396</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1915321940</t>
+          <t>https://m.place.naver.com/place/813673396</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2064,30 +2064,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>미라클비뇨기과의원</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>더율피부과의원</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>theyulderma@naver.com</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>032-572-8275</t>
+          <t>032-225-2223</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 363 3층 미라클</t>
+          <t>인천광역시 서구 중봉대로 588 406호, 407호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://the-yul.co.kr/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2097,7 +2101,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2108,7 +2112,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2117,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>484</v>
+        <v>398</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="R18" t="n">
-        <v>485</v>
+        <v>598</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2136,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13137484</t>
+          <t>1246412735</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13137484</t>
+          <t>https://m.place.naver.com/place/1246412735</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2154,29 +2158,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>닥터에버스의원 청라</t>
+          <t>휴먼피부과의원 청라점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>drevers777@naver.com</t>
+          <t>human___ch@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1411-8830</t>
+          <t>032-283-3335</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미센텀시티 10층 1036호</t>
+          <t>인천광역시 서구 중봉대로 594 청라비전프라자 4층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://evers7.co.kr/</t>
+          <t>http://www.humanic.co.kr</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2191,7 +2195,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2211,13 +2215,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1293</v>
+        <v>2926</v>
       </c>
       <c r="Q19" t="n">
-        <v>1286</v>
+        <v>1098</v>
       </c>
       <c r="R19" t="n">
-        <v>2579</v>
+        <v>4024</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,17 +2230,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1008759002</t>
+          <t>1835204658</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008759002</t>
+          <t>https://m.place.naver.com/place/1835204658</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2248,34 +2252,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>현대아이비의원</t>
+          <t>청라브이의원</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>hdib0754@naver.com</t>
+          <t>cnvclinic@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1405-0754</t>
+          <t>032-567-8258</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 서구 탁옥로 45 3층</t>
+          <t>인천광역시 서구 청라커낼로260번길 7-11 퍼스트타워 2층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://www.ibclinic.co.kr/</t>
+          <t>https://tinyurl.com/mr4enztn</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2285,7 +2289,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2296,22 +2300,22 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>384</v>
+        <v>917</v>
       </c>
       <c r="Q20" t="n">
-        <v>74</v>
+        <v>568</v>
       </c>
       <c r="R20" t="n">
-        <v>458</v>
+        <v>1485</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,17 +2324,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>32839994</t>
+          <t>1958745925</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32839994</t>
+          <t>https://m.place.naver.com/place/1958745925</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2399,13 +2403,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="Q21" t="n">
         <v>9</v>
       </c>
       <c r="R21" t="n">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2424,7 +2428,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2436,34 +2440,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>서유컴퍼니</t>
+          <t>밸런스마케팅</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>luvcho90@naver.com</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>dailyn012@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>bmg9449@gmail.com</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1415-5663</t>
+          <t>0507-1448-9449</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 9-11 219호</t>
+          <t>인천광역시 서구 청라라임로 109</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://balmkt.com</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2473,7 +2481,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2484,7 +2492,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2496,10 +2504,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,17 +2516,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2051154317</t>
+          <t>1427212703</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051154317</t>
+          <t>https://m.place.naver.com/place/1427212703</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2530,34 +2538,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>밸런스마케팅</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>bmg9449@gmail.com</t>
-        </is>
-      </c>
+          <t>서유컴퍼니</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>luvcho90@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1448-9449</t>
+          <t>0507-1415-5663</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 109</t>
+          <t>인천광역시 서구 중봉대로586번길 9-11 219호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://balmkt.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2567,7 +2575,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2578,7 +2586,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2590,10 +2598,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,17 +2610,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1427212703</t>
+          <t>2051154317</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1427212703</t>
+          <t>https://m.place.naver.com/place/2051154317</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2624,44 +2632,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>우리베스트내과의원</t>
+          <t>청라건강한내과의원</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>wooribesthealth@naver.com</t>
+          <t>kuku337@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>032-715-6308</t>
+          <t>032-567-8009</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 15 4층</t>
+          <t>인천광역시 서구 청라라임로 71 5층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://wooribestmed.co.kr/</t>
+          <t>http://www.healthyclinic.kr/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2672,22 +2680,22 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1964</v>
+        <v>431</v>
       </c>
       <c r="Q24" t="n">
-        <v>212</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>2176</v>
+        <v>432</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,17 +2704,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1134694701</t>
+          <t>32349771</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134694701</t>
+          <t>https://m.place.naver.com/place/32349771</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2718,25 +2726,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>청라바른내과의원</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>우리베스트내과의원</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>wooribesthealth@naver.com</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>032-562-8575</t>
+          <t>032-715-6308</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로161번길 3-5 청라빌딩 2, 3, 4층</t>
+          <t>인천광역시 서구 염곡로464번길 15 4층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.chbareun.co.kr</t>
+          <t>http://wooribestmed.co.kr/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2751,7 +2763,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2762,22 +2774,22 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>147</v>
+        <v>1964</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>212</v>
       </c>
       <c r="R25" t="n">
-        <v>151</v>
+        <v>2176</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2798,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1717084209</t>
+          <t>1134694701</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1717084209</t>
+          <t>https://m.place.naver.com/place/1134694701</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2808,25 +2820,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>청라나눔내과의원</t>
+          <t>청라바른내과의원</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1404-0750</t>
+          <t>032-562-8575</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 90 MK뷰 빌딩 5층</t>
+          <t>인천광역시 서구 청라한내로161번길 3-5 청라빌딩 2, 3, 4층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://www.nanum-clinic.com</t>
+          <t>https://www.chbareun.co.kr</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2857,17 +2869,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>917</v>
+        <v>147</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>925</v>
+        <v>151</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,17 +2888,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>37629322</t>
+          <t>1717084209</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37629322</t>
+          <t>https://m.place.naver.com/place/1717084209</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2898,29 +2910,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>다정한내과의원</t>
+          <t>서울삼성의원</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dajunghanim22@naver.com</t>
+          <t>comwel2009@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1349-7511</t>
+          <t>032-564-9970</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 81 2층</t>
+          <t>인천광역시 서구 중봉대로 587 지하2층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dajunghanim22</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2930,12 +2942,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2955,13 +2967,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>641</v>
+        <v>613</v>
       </c>
       <c r="Q27" t="n">
-        <v>199</v>
+        <v>14</v>
       </c>
       <c r="R27" t="n">
-        <v>840</v>
+        <v>627</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,17 +2982,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>38270484</t>
+          <t>36477012</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38270484</t>
+          <t>https://m.place.naver.com/place/36477012</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2992,29 +3004,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>서울삼성의원</t>
+          <t>다정한내과의원</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>drgkjin9@naver.com</t>
+          <t>dajunghanim22@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>032-564-9970</t>
+          <t>0507-1349-7511</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 587 지하2층</t>
+          <t>인천광역시 서구 청라루비로 81 2층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dajunghanim22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3024,12 +3036,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3049,13 +3061,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>611</v>
+        <v>641</v>
       </c>
       <c r="Q28" t="n">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="R28" t="n">
-        <v>625</v>
+        <v>841</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,56 +3076,56 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>36477012</t>
+          <t>38270484</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36477012</t>
+          <t>https://m.place.naver.com/place/38270484</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>동물병원</t>
+          <t>내과</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>코지동물의료센터 인천서구청점</t>
+          <t>청라나눔내과의원</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>cozyamc@naver.com</t>
+          <t>gawai31@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1471-7558</t>
+          <t>0507-1404-0750</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 263 1층</t>
+          <t>인천광역시 서구 청라한내로 90 MK뷰 빌딩 5층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/profile/wyb2ld7</t>
+          <t>http://www.nanum-clinic.com</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3128,14 +3140,10 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/profile</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>X</t>
@@ -3147,13 +3155,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>366</v>
+        <v>918</v>
       </c>
       <c r="Q29" t="n">
-        <v>426</v>
+        <v>8</v>
       </c>
       <c r="R29" t="n">
-        <v>792</v>
+        <v>926</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,51 +3170,51 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1925951270</t>
+          <t>37629322</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1925951270</t>
+          <t>https://m.place.naver.com/place/37629322</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>병원,의원</t>
+          <t>동물병원</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>청라이엠365의원</t>
+          <t>코지동물의료센터 인천서구청점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>em365cn@naver.com</t>
+          <t>cozyamc@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>032-564-0911</t>
+          <t>0507-1471-7558</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 24 202~205, 301~305호</t>
+          <t>인천광역시 서구 서곶로 263 1층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://cnem365.co.kr/</t>
+          <t>https://talk.naver.com/profile/wyb2ld7</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3216,20 +3224,24 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>X</t>
@@ -3237,17 +3249,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>255</v>
+        <v>367</v>
       </c>
       <c r="Q30" t="n">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="R30" t="n">
-        <v>663</v>
+        <v>791</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,17 +3268,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1610105439</t>
+          <t>1925951270</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1610105439</t>
+          <t>https://m.place.naver.com/place/1925951270</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3281,11 +3293,7 @@
           <t>미스토리의원</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>cherry3559@naver.com</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -3360,7 +3368,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3372,40 +3380,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>진이비인후과의원</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>청라이엠365의원</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>em365cn@naver.com</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>032-561-5552</t>
+          <t>032-564-0911</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 4층 403, 404호</t>
+          <t>인천광역시 서구 청라한내로100번길 24 202~205, 301~305호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://jeanhearing.co.kr/</t>
+          <t>https://cnem365.co.kr/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3425,13 +3437,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>199</v>
+        <v>258</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>413</v>
       </c>
       <c r="R32" t="n">
-        <v>201</v>
+        <v>671</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3440,51 +3452,51 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1019090921</t>
+          <t>1610105439</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1019090921</t>
+          <t>https://m.place.naver.com/place/1610105439</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>병원부속시설</t>
+          <t>병원,의원</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>소통부부한의원 청라 피부미용클리닉</t>
+          <t>진이비인후과의원</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>et_news@naver.com</t>
+          <t>chk40366@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>032-710-1473</t>
+          <t>032-561-5552</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 65 라임타워 8층</t>
+          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 4층 403, 404호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sotongbeauty</t>
+          <t>https://jeanhearing.co.kr/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3515,17 +3527,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>365</v>
+        <v>199</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>365</v>
+        <v>201</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3534,52 +3546,56 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2046680647</t>
+          <t>1019090921</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2046680647</t>
+          <t>https://m.place.naver.com/place/1019090921</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>비뇨의학과</t>
+          <t>병원부속시설</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>엘림비뇨기과의원</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>소통부부한의원 청라 피부미용클리닉</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>et_news@naver.com</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>032-577-7533</t>
+          <t>032-710-1473</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 308 석남프라자</t>
+          <t>인천광역시 서구 청라라임로 65 라임타워 7층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://www.elimuro.com/</t>
+          <t>https://www.instagram.com/sotongbeauty</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3605,17 +3621,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>173</v>
+        <v>428</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>174</v>
+        <v>428</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3624,17 +3640,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>11607252</t>
+          <t>2046680647</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11607252</t>
+          <t>https://m.place.naver.com/place/2046680647</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3646,40 +3662,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>라임비뇨의학과의원 청라점</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>루원삼성비뇨의학과의원</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>lu1samsung@naver.com</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1438-5388</t>
+          <t>032-565-0728</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 594 504~505호</t>
+          <t>인천광역시 서구 봉오재3로 90</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://limeurology10.co.kr</t>
+          <t>https://blog.naver.com/lu1samsung</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3690,7 +3710,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3699,13 +3719,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="Q35" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>208</v>
+        <v>119</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3714,61 +3734,61 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>35593344</t>
+          <t>1166037095</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35593344</t>
+          <t>https://m.place.naver.com/place/1166037095</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>성형외과</t>
+          <t>비뇨의학과</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>명메디칼스킨남성의원</t>
+          <t>엘림비뇨기과의원</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>flalswnwn@naver.com</t>
+          <t>binterest@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>032-561-7564</t>
+          <t>032-577-7533</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 364-1 창대빌딩</t>
+          <t>인천광역시 서구 가정로 308 석남프라자</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.elimuro.com/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3793,13 +3813,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>55</v>
+        <v>173</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3808,51 +3828,51 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>19513442</t>
+          <t>11607252</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19513442</t>
+          <t>https://m.place.naver.com/place/11607252</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>소아청소년과</t>
+          <t>비뇨의학과</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>사랑소아청소년과의원</t>
+          <t>라임비뇨의학과의원 청라점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>srpc0610@naver.com</t>
+          <t>gentleman_repair@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1366-8277</t>
+          <t>0507-1438-5388</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 서구 새오개로111번안길 31 도모빌딩2층 사랑소아청소년과</t>
+          <t>인천광역시 서구 중봉대로 594 504~505호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://short.ddocdoc.com/2b2vhj</t>
+          <t>http://limeurology10.co.kr</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3878,7 +3898,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3887,13 +3907,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="R37" t="n">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,46 +3922,42 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1324399229</t>
+          <t>35593344</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324399229</t>
+          <t>https://m.place.naver.com/place/35593344</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>소아청소년과</t>
+          <t>성형외과</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>마트소아청소년과의원</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>mylovewoo5@naver.com</t>
-        </is>
-      </c>
+          <t>명메디칼스킨남성의원</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>032-568-6977</t>
+          <t>032-561-7564</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 252</t>
+          <t>인천광역시 서구 가정로 364-1 창대빌딩</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3981,13 +3997,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="Q38" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>143</v>
+        <v>56</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3996,17 +4012,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>32264367</t>
+          <t>19513442</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32264367</t>
+          <t>https://m.place.naver.com/place/19513442</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4037,11 @@
           <t>아이비소아청소년과의원</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>happysofa_net@naver.com</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
@@ -4096,7 +4116,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4108,40 +4128,44 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>아이사랑소아청소년과의원</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>청라미소소아청소년과의원</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>misoped_clinic@naver.com</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>032-561-0279</t>
+          <t>032-563-7227</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 40 202호</t>
+          <t>인천광역시 서구 청라커낼로288번길 10 505호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://iloveped.medisay.co.kr</t>
+          <t>https://blog.naver.com/misoped_clinic</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4161,13 +4185,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>171</v>
+        <v>94</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>177</v>
+        <v>103</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4176,17 +4200,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1089940606</t>
+          <t>1965538592</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089940606</t>
+          <t>https://m.place.naver.com/place/1965538592</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4198,44 +4222,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>청라미소소아청소년과의원</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>misoped_clinic@naver.com</t>
-        </is>
-      </c>
+          <t>아이사랑소아청소년과의원</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>032-563-7227</t>
+          <t>032-561-0279</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 10 505호</t>
+          <t>인천광역시 서구 봉오재3로 40 202호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/misoped_clinic</t>
+          <t>https://iloveped.medisay.co.kr</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4255,13 +4275,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>94</v>
+        <v>171</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R41" t="n">
-        <v>103</v>
+        <v>177</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4270,17 +4290,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1965538592</t>
+          <t>1089940606</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965538592</t>
+          <t>https://m.place.naver.com/place/1089940606</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4292,29 +4312,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>해맑은소아청소년과의원</t>
+          <t>청라튼튼소아청소년과의원</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>aidaot3@naver.com</t>
+          <t>luwon365@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>032-569-7588</t>
+          <t>032-564-5955</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71</t>
+          <t>인천광역시 서구 솔빛로 24 부영프라자 201호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://brightped.co.kr/index.asp</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4324,7 +4344,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4349,13 +4369,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="Q42" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
-        <v>167</v>
+        <v>405</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4364,17 +4384,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>20107762</t>
+          <t>35516433</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20107762</t>
+          <t>https://m.place.naver.com/place/35516433</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4409,11 @@
           <t>365별소아청소년과의원</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>dygks0823@naver.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
@@ -4442,10 +4466,10 @@
         <v>1100</v>
       </c>
       <c r="Q43" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R43" t="n">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4464,41 +4488,41 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>소아청소년과</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>청라센트럴안과의원</t>
+          <t>사랑소아청소년과의원</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>centraleyeclinic@naver.com</t>
+          <t>twoulike@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>032-582-0079</t>
+          <t>0507-1366-8277</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로74번길 31 월드프라자 5층 501호</t>
+          <t>인천광역시 서구 새오개로111번안길 31 도모빌딩2층 사랑소아청소년과</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://www.central-eye.co.kr/</t>
+          <t>https://short.ddocdoc.com/2b2vhj</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4508,12 +4532,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4533,13 +4557,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1210</v>
+        <v>107</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>1220</v>
+        <v>110</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4548,51 +4572,51 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>765893138</t>
+          <t>1324399229</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/765893138</t>
+          <t>https://m.place.naver.com/place/1324399229</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>이비인후과</t>
+          <t>소아청소년과</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>코아이비인후과의원</t>
+          <t>해맑은소아청소년과의원</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>coaent75@naver.com</t>
+          <t>aidaot3@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>032-575-7582</t>
+          <t>032-569-7588</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 588 청라센트럴프라자 3층</t>
+          <t>인천광역시 서구 청라라임로 71</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://coaclinic.net/</t>
+          <t>http://brightped.co.kr/index.asp</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4618,7 +4642,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4627,13 +4651,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1165</v>
+        <v>150</v>
       </c>
       <c r="Q45" t="n">
         <v>17</v>
       </c>
       <c r="R45" t="n">
-        <v>1182</v>
+        <v>167</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4642,56 +4666,56 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>21331263</t>
+          <t>20107762</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21331263</t>
+          <t>https://m.place.naver.com/place/20107762</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>이비인후과</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>열린이비인후과의원</t>
+          <t>청라센트럴안과의원</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>letmeshow111@naver.com</t>
+          <t>centraleyeclinic@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>032-565-0938</t>
+          <t>032-582-0079</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 44 명문프라자 2층</t>
+          <t>인천광역시 서구 크리스탈로74번길 31 월드프라자 5층 501호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/letmeshow111</t>
+          <t>http://www.central-eye.co.kr/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4721,13 +4745,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>630</v>
+        <v>1210</v>
       </c>
       <c r="Q46" t="n">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="R46" t="n">
-        <v>724</v>
+        <v>1220</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4736,17 +4760,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>888152498</t>
+          <t>765893138</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/888152498</t>
+          <t>https://m.place.naver.com/place/765893138</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4758,44 +4782,44 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>율 이비인후과 의원</t>
+          <t>상이비인후과</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>yul_ent@naver.com</t>
+          <t>hjmi4686@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1349-4606</t>
+          <t>032-572-7582</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 96 3층 303, 304, 305호</t>
+          <t>인천광역시 서구 가정로 372 2층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.yulent.net</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4815,13 +4839,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>49</v>
+        <v>313</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>49</v>
+        <v>317</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4830,17 +4854,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2061001738</t>
+          <t>13240086</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061001738</t>
+          <t>https://m.place.naver.com/place/13240086</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4852,29 +4876,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>열린성모이비인후과의원</t>
+          <t>열린이비인후과의원</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>rrkdkjh@naver.com</t>
+          <t>letmeshow111@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>032-885-8275</t>
+          <t>032-565-0938</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 진영메디피아 5층 열린성모이비인후과</t>
+          <t>인천광역시 서구 봉오재3로 44 명문프라자 2층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/letmeshow111</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4884,12 +4908,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4909,13 +4933,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>359</v>
+        <v>633</v>
       </c>
       <c r="Q48" t="n">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="R48" t="n">
-        <v>362</v>
+        <v>731</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4924,17 +4948,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>36728069</t>
+          <t>888152498</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36728069</t>
+          <t>https://m.place.naver.com/place/888152498</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4946,40 +4970,44 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>상이비인후과</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>율 이비인후과 의원</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>yul_ent@naver.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>032-572-7582</t>
+          <t>0507-1349-4606</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 372 2층</t>
+          <t>인천광역시 서구 청라한내로 96 3층 303, 304, 305호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.yulent.net</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4999,13 +5027,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>313</v>
+        <v>49</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>317</v>
+        <v>49</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5014,56 +5042,52 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>13240086</t>
+          <t>2061001738</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240086</t>
+          <t>https://m.place.naver.com/place/2061001738</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>정형외과</t>
+          <t>이비인후과</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>가정성모의원</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>gajeongsungmo@naver.com</t>
-        </is>
-      </c>
+          <t>열린성모이비인후과의원</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1390-7586</t>
+          <t>032-885-8275</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청중로 486 부일프라자 3, 4층</t>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 5층 열린성모이비인후과</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://gajeongsm.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5093,13 +5117,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="Q50" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="R50" t="n">
-        <v>399</v>
+        <v>362</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5108,51 +5132,51 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>38674023</t>
+          <t>36728069</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38674023</t>
+          <t>https://m.place.naver.com/place/36728069</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>정형외과</t>
+          <t>이비인후과</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>진정형외과의원</t>
+          <t>코아이비인후과의원</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>lovehosp@naver.com</t>
+          <t>coaent75@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>032-566-0085</t>
+          <t>032-575-7582</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 264 403~404호</t>
+          <t>인천광역시 서구 중봉대로 588 청라센트럴프라자 3층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://coaclinic.net/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5162,7 +5186,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5178,7 +5202,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5187,13 +5211,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>267</v>
+        <v>1165</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="R51" t="n">
-        <v>272</v>
+        <v>1182</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5202,17 +5226,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>38667983</t>
+          <t>21331263</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38667983</t>
+          <t>https://m.place.naver.com/place/21331263</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5251,11 @@
           <t>제대로정형외과마취통증의학과의원</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>astondis@naver.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
@@ -5302,7 +5330,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5314,29 +5342,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>드림재활의학과의원</t>
+          <t>진정형외과의원</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>sand14287@naver.com</t>
+          <t>lovehosp@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1405-7177</t>
+          <t>032-566-0085</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 588</t>
+          <t>인천광역시 서구 청라커낼로 264 403~404호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sand14287</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5346,12 +5374,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5371,13 +5399,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="Q53" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5386,17 +5414,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>32473115</t>
+          <t>38667983</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32473115</t>
+          <t>https://m.place.naver.com/place/38667983</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5411,11 +5439,7 @@
           <t>청라성모정형외과의원</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>daily_beut2@naver.com</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
@@ -5490,46 +5514,42 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>한방병원</t>
+          <t>정형외과</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>서인천한방병원</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>chtjdus@naver.com</t>
-        </is>
-      </c>
+          <t>가정성모의원</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>032-521-7582</t>
+          <t>0507-1390-7586</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 7 6층 서인천한방병원</t>
+          <t>인천광역시 서구 청중로 486 부일프라자 3, 4층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://gajeongsm.co.kr</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5559,13 +5579,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>205</v>
+        <v>330</v>
       </c>
       <c r="Q55" t="n">
-        <v>856</v>
+        <v>70</v>
       </c>
       <c r="R55" t="n">
-        <v>1061</v>
+        <v>400</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5574,61 +5594,61 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1042604346</t>
+          <t>38674023</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1042604346</t>
+          <t>https://m.place.naver.com/place/38674023</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>한방병원</t>
+          <t>정형외과</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>청라좋은한방병원</t>
+          <t>드림재활의학과의원</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jjlee1117@naver.com</t>
+          <t>sand14287@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>032-568-2005</t>
+          <t>0507-1405-7177</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 2층~4층</t>
+          <t>인천광역시 서구 중봉대로 588</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://cn-hani.co.kr/</t>
+          <t>https://blog.naver.com/sand14287</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5644,7 +5664,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5653,13 +5673,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>586</v>
+        <v>238</v>
       </c>
       <c r="Q56" t="n">
-        <v>1203</v>
+        <v>41</v>
       </c>
       <c r="R56" t="n">
-        <v>1789</v>
+        <v>279</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5668,17 +5688,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2095160385</t>
+          <t>32473115</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095160385</t>
+          <t>https://m.place.naver.com/place/32473115</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5721,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>032-719-8258</t>
+          <t>0507-1343-8258</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -5747,13 +5767,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="Q57" t="n">
-        <v>3082</v>
+        <v>3174</v>
       </c>
       <c r="R57" t="n">
-        <v>3750</v>
+        <v>3866</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5772,7 +5792,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5784,29 +5804,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>인정한방병원</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>haecare@naver.com</t>
-        </is>
-      </c>
+          <t>청라좋은한방병원</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1356-7782</t>
+          <t>032-568-2005</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 B동 5층</t>
+          <t>인천광역시 서구 청라에메랄드로 79 2층~4층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.injungmedi.com</t>
+          <t>http://cn-hani.co.kr/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5841,13 +5857,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>184</v>
+        <v>613</v>
       </c>
       <c r="Q58" t="n">
-        <v>927</v>
+        <v>1127</v>
       </c>
       <c r="R58" t="n">
-        <v>1111</v>
+        <v>1740</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5856,51 +5872,51 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1428648030</t>
+          <t>2095160385</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1428648030</t>
+          <t>https://m.place.naver.com/place/2095160385</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>한의원</t>
+          <t>한방병원</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>청라함소아한의원</t>
+          <t>서인천한방병원</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>cn_hamsoa@naver.com</t>
+          <t>chtjdus@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1497-1331</t>
+          <t>032-521-7582</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 94 3층</t>
+          <t>인천광역시 서구 염곡로464번길 7 6층 서인천한방병원</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cn_hamsoa</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5910,12 +5926,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5931,17 +5947,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="Q59" t="n">
-        <v>20</v>
+        <v>871</v>
       </c>
       <c r="R59" t="n">
-        <v>232</v>
+        <v>1078</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5950,51 +5966,51 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>30811670</t>
+          <t>1042604346</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30811670</t>
+          <t>https://m.place.naver.com/place/1042604346</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>한의원</t>
+          <t>한방병원</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>일등한의원 인천가정</t>
+          <t>인정한방병원</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ildungno1@naver.com</t>
+          <t>haecare@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>032-710-3969</t>
+          <t>0507-1356-7782</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 378 2층</t>
+          <t>인천광역시 서구 청라에메랄드로 99 B동 5층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rNPHb</t>
+          <t>https://www.injungmedi.com</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6004,12 +6020,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6029,13 +6045,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1953</v>
+        <v>185</v>
       </c>
       <c r="Q60" t="n">
-        <v>1255</v>
+        <v>926</v>
       </c>
       <c r="R60" t="n">
-        <v>3208</v>
+        <v>1111</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6044,17 +6060,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1608876929</t>
+          <t>1428648030</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1608876929</t>
+          <t>https://m.place.naver.com/place/1428648030</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6066,44 +6082,44 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>단비한의원</t>
+          <t>경희명한의원</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>danbimkv@naver.com</t>
+          <t>ymungz@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1481-1081</t>
+          <t>0507-1399-8123</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 90 엠케이뷰 6층 단비한의원</t>
+          <t>인천광역시 서구 푸른로 3 2층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/danbImkv</t>
+          <t>http://www.koreamedicine.co.kr</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6119,17 +6135,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="Q61" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="R61" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6138,17 +6154,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1068245349</t>
+          <t>13238392</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1068245349</t>
+          <t>https://m.place.naver.com/place/13238392</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6160,29 +6176,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>대가침 한의원</t>
+          <t>단비한의원</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>brandbondam@naver.com</t>
+          <t>danbimkv@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1392-7604</t>
+          <t>0507-1481-1081</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 398 3층 301호</t>
+          <t>인천광역시 서구 청라한내로 90 엠케이뷰 6층 단비한의원</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/danbImkv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6192,7 +6208,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6213,17 +6229,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>525</v>
+        <v>220</v>
       </c>
       <c r="Q62" t="n">
-        <v>542</v>
+        <v>50</v>
       </c>
       <c r="R62" t="n">
-        <v>1067</v>
+        <v>270</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6232,17 +6248,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1196340303</t>
+          <t>1068245349</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1196340303</t>
+          <t>https://m.place.naver.com/place/1068245349</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6254,29 +6270,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>사랑이꽃피는한의원</t>
+          <t>뜰한의원</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>5551199@naver.com</t>
+          <t>gardenhani@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>032-555-1199</t>
+          <t>0507-1473-1472</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 280 골든프라자 3층</t>
+          <t>인천광역시 서구 청라커낼로288번길 10 4층 406호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5551199</t>
+          <t>https://blog.naver.com/gardenhani</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6307,17 +6323,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>317</v>
+        <v>222</v>
       </c>
       <c r="Q63" t="n">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="R63" t="n">
-        <v>353</v>
+        <v>325</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6326,17 +6342,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>11599722</t>
+          <t>1152812855</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11599722</t>
+          <t>https://m.place.naver.com/place/1152812855</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6348,29 +6364,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>루원365한의원 인천가정역점</t>
+          <t>일등한의원 인천가정</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>leesak0310@naver.com</t>
+          <t>ildungno1@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1323-4975</t>
+          <t>032-710-3969</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 15 쓰리엠타워 3층</t>
+          <t>인천광역시 서구 가정로 378 2층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://www.ru1.kr</t>
+          <t>http://pf.kakao.com/_rNPHb</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6405,13 +6421,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>858</v>
+        <v>2002</v>
       </c>
       <c r="Q64" t="n">
-        <v>597</v>
+        <v>1253</v>
       </c>
       <c r="R64" t="n">
-        <v>1455</v>
+        <v>3255</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6420,17 +6436,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1264346896</t>
+          <t>1608876929</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264346896</t>
+          <t>https://m.place.naver.com/place/1608876929</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6442,25 +6458,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>본아루 한의원</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>강경하한의원</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>lies9653@naver.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1411-5966</t>
+          <t>0507-1489-7904</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 437 301동 112호</t>
+          <t>인천광역시 서구 중봉대로 610 청라 마루힐프라자 2층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://kkh-clinic.com/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6470,12 +6490,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6486,7 +6506,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6495,13 +6515,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>100</v>
+        <v>498</v>
       </c>
       <c r="Q65" t="n">
-        <v>548</v>
+        <v>2268</v>
       </c>
       <c r="R65" t="n">
-        <v>648</v>
+        <v>2766</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6510,17 +6530,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2097552892</t>
+          <t>251851306</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2097552892</t>
+          <t>https://m.place.naver.com/place/251851306</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6532,29 +6552,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>청라단비한의원</t>
+          <t>청라맑은샘한의원 청라</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>4bazdanbi@naver.com</t>
+          <t>mfxignhacq955@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>032-565-1075</t>
+          <t>0507-1364-1240</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로102번길 8</t>
+          <t>인천광역시 서구 청라루비로 93 루비타워 205호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://www.4baz.com/renewal/info/network.php?nc=36</t>
+          <t>https://youtu.be/bwEb-MbSvTg?si=qywW0LXKoCEcRhN3</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6564,12 +6584,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6589,13 +6609,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>87</v>
+        <v>953</v>
       </c>
       <c r="Q66" t="n">
-        <v>86</v>
+        <v>1034</v>
       </c>
       <c r="R66" t="n">
-        <v>173</v>
+        <v>1987</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6604,17 +6624,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1436746799</t>
+          <t>1161608478</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1436746799</t>
+          <t>https://m.place.naver.com/place/1161608478</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6626,29 +6646,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>청라 리아한의원</t>
+          <t>이주한의원</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>wlsdudtn04@naver.com</t>
+          <t>leejookmc@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1372-4975</t>
+          <t>032-719-7565</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-17 청라타워돔 3층 리아한의원</t>
+          <t>인천광역시 서구 청라라임로 85 청라린스트라우스 A동 206호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wlsdudtn04</t>
+          <t>https://blog.naver.com/leejookmc</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6683,13 +6703,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>420</v>
+        <v>74</v>
       </c>
       <c r="Q67" t="n">
-        <v>2081</v>
+        <v>59</v>
       </c>
       <c r="R67" t="n">
-        <v>2501</v>
+        <v>133</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6698,17 +6718,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>37485905</t>
+          <t>1421602346</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37485905</t>
+          <t>https://m.place.naver.com/place/1421602346</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6720,34 +6740,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>청라맑은샘한의원 청라</t>
+          <t>루원365한의원 인천가정역점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>eudkjmlpcg545@naver.com</t>
+          <t>leesak0310@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1364-1240</t>
+          <t>0507-1323-4975</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 93 루비타워 205호</t>
+          <t>인천광역시 서구 염곡로464번길 15 쓰리엠타워 3층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://youtu.be/bwEb-MbSvTg?si=qywW0LXKoCEcRhN3</t>
+          <t>http://www.ru1.kr</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6768,7 +6788,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6777,13 +6797,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>953</v>
+        <v>863</v>
       </c>
       <c r="Q68" t="n">
-        <v>1016</v>
+        <v>601</v>
       </c>
       <c r="R68" t="n">
-        <v>1969</v>
+        <v>1464</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6792,17 +6812,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1161608478</t>
+          <t>1264346896</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161608478</t>
+          <t>https://m.place.naver.com/place/1264346896</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6814,29 +6834,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>라원한의원</t>
+          <t>청라함소아한의원</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>rawonkmc@naver.com</t>
+          <t>cn_hamsoa@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>032-710-7595</t>
+          <t>0507-1497-1331</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로74번길 31 월드프라자 3층 304호</t>
+          <t>인천광역시 서구 청라에메랄드로 94 3층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rawonkmc</t>
+          <t>https://blog.naver.com/cn_hamsoa</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6867,17 +6887,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>103</v>
+        <v>212</v>
       </c>
       <c r="Q69" t="n">
-        <v>711</v>
+        <v>20</v>
       </c>
       <c r="R69" t="n">
-        <v>814</v>
+        <v>232</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6886,17 +6906,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2096190859</t>
+          <t>30811670</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2096190859</t>
+          <t>https://m.place.naver.com/place/30811670</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6908,34 +6928,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>정본한의원</t>
+          <t>본아루 한의원</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>sangkakim1@naver.com</t>
+          <t>bonearu@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1394-8004</t>
+          <t>0507-1411-5966</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 379 진원빌딩 4층 402호</t>
+          <t>인천광역시 서구 가정로 437 301동 112호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.jeongbone.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6945,7 +6965,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6961,17 +6981,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1089</v>
+        <v>100</v>
       </c>
       <c r="Q70" t="n">
-        <v>2640</v>
+        <v>452</v>
       </c>
       <c r="R70" t="n">
-        <v>3729</v>
+        <v>552</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6980,17 +7000,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1623452423</t>
+          <t>2097552892</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623452423</t>
+          <t>https://m.place.naver.com/place/2097552892</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7059,13 +7079,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q71" t="n">
-        <v>1507</v>
+        <v>1415</v>
       </c>
       <c r="R71" t="n">
-        <v>1710</v>
+        <v>1620</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7084,7 +7104,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7096,39 +7116,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>경희명한의원</t>
+          <t>라원한의원</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ymungz@naver.com</t>
+          <t>rawonkmc@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1399-8123</t>
+          <t>032-710-7595</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 서구 푸른로 3 2층</t>
+          <t>인천광역시 서구 크리스탈로74번길 31 월드프라자 3층 304호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://www.koreamedicine.co.kr</t>
+          <t>https://blog.naver.com/rawonkmc</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7153,13 +7173,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>257</v>
+        <v>111</v>
       </c>
       <c r="Q72" t="n">
-        <v>7</v>
+        <v>492</v>
       </c>
       <c r="R72" t="n">
-        <v>264</v>
+        <v>603</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7168,17 +7188,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>13238392</t>
+          <t>2096190859</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13238392</t>
+          <t>https://m.place.naver.com/place/2096190859</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7190,39 +7210,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>뜰한의원</t>
+          <t>정본한의원</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>gardenhani@naver.com</t>
+          <t>sangkakim1@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1473-1472</t>
+          <t>0507-1394-8004</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 10 4층 406호</t>
+          <t>인천광역시 서구 가정로 379 진원빌딩 4층 402호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gardenhani</t>
+          <t>https://www.jeongbone.com</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7243,17 +7263,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>221</v>
+        <v>1093</v>
       </c>
       <c r="Q73" t="n">
-        <v>102</v>
+        <v>2753</v>
       </c>
       <c r="R73" t="n">
-        <v>323</v>
+        <v>3846</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7262,17 +7282,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1152812855</t>
+          <t>1623452423</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1152812855</t>
+          <t>https://m.place.naver.com/place/1623452423</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7284,44 +7304,44 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>신농씨한의원</t>
+          <t>소통부부한의원 청라</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>shinnong71@naver.com</t>
+          <t>sotongbbcn@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1330-1075</t>
+          <t>0507-1498-3420</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 505호 신농씨한의원</t>
+          <t>인천광역시 서구 청라라임로 65 4층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/shinnong71</t>
+          <t>http://www.sotongbooboo.co.kr/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7332,22 +7352,22 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1155</v>
+        <v>1644</v>
       </c>
       <c r="Q74" t="n">
-        <v>235</v>
+        <v>3502</v>
       </c>
       <c r="R74" t="n">
-        <v>1390</v>
+        <v>5146</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7356,17 +7376,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>21039223</t>
+          <t>35734767</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21039223</t>
+          <t>https://m.place.naver.com/place/35734767</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7378,29 +7398,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>강경하한의원</t>
+          <t>청라 리아한의원</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>lies9653@naver.com</t>
+          <t>wlsdudtn04@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1489-7904</t>
+          <t>0507-1372-4975</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 610 청라 마루힐프라자 2층</t>
+          <t>인천광역시 서구 중봉대로612번길 10-17 청라타워돔 3층 리아한의원</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://kkh-clinic.com/</t>
+          <t>https://blog.naver.com/wlsdudtn04</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7426,7 +7446,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7435,13 +7455,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>499</v>
+        <v>430</v>
       </c>
       <c r="Q75" t="n">
-        <v>2229</v>
+        <v>2120</v>
       </c>
       <c r="R75" t="n">
-        <v>2728</v>
+        <v>2550</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7450,17 +7470,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>251851306</t>
+          <t>37485905</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/251851306</t>
+          <t>https://m.place.naver.com/place/37485905</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7472,44 +7492,44 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>소통부부한의원 청라</t>
+          <t>신농씨한의원</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sotongbbcn@naver.com</t>
+          <t>shinnong71@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1498-3420</t>
+          <t>0507-1330-1075</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 65 4층</t>
+          <t>인천광역시 서구 청라라임로 71 505호 신농씨한의원</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://www.sotongbooboo.co.kr/</t>
+          <t>https://blog.naver.com/shinnong71</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7520,22 +7540,22 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1628</v>
+        <v>1158</v>
       </c>
       <c r="Q76" t="n">
-        <v>3481</v>
+        <v>235</v>
       </c>
       <c r="R76" t="n">
-        <v>5109</v>
+        <v>1393</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7544,17 +7564,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>35734767</t>
+          <t>21039223</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35734767</t>
+          <t>https://m.place.naver.com/place/21039223</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_derma/청라_피부과.xlsx
+++ b/naver-place-crawler/results_derma/청라_피부과.xlsx
@@ -423,7 +423,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>이너스피부과의원</t>
+          <t>미엘피부과의원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>laugh5ne@naver.com</t>
+          <t>mielskin@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>032-262-1777</t>
+          <t>032-572-7111</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 281 자혜빌딩 3층</t>
+          <t>인천광역시 서구 가정로 375 403, 404호 금강아미움</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://ic.mielskin.co.kr/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>361</v>
+        <v>1518</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>361</v>
+        <v>1521</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>36428624</t>
+          <t>1405806250</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428624</t>
+          <t>https://m.place.naver.com/place/1405806250</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -666,11 +666,7 @@
           <t>cleanup-cr@naver.com</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>promotion@cunetwork.co.kr</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>0507-1421-7590</t>
@@ -689,17 +685,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,10 +718,10 @@
         <v>715</v>
       </c>
       <c r="Q3" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="R3" t="n">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -759,11 +755,7 @@
           <t>청라의원</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>cnvclinic@naver.com</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
@@ -838,7 +830,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -850,34 +842,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>고운의원</t>
+          <t>서울더본피부과의원</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>thegounclinic@naver.com</t>
+          <t>darguji@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1496-2806</t>
+          <t>032-710-0075</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 거북로 98 3층</t>
+          <t>인천광역시 서구 중봉대로586번길 9-4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://seoulderborn.com</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -887,7 +879,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,17 +895,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>74</v>
+        <v>823</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R5" t="n">
-        <v>78</v>
+        <v>832</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13240170</t>
+          <t>1062309841</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240170</t>
+          <t>https://m.place.naver.com/place/1062309841</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -944,29 +936,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>현대아이비의원</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>hdib0754@naver.com</t>
-        </is>
-      </c>
+          <t>고운의원</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1405-0754</t>
+          <t>0507-1496-2806</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 탁옥로 45 3층</t>
+          <t>인천광역시 서구 거북로 98 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.ibclinic.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,12 +964,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1001,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>384</v>
+        <v>74</v>
       </c>
       <c r="Q6" t="n">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>458</v>
+        <v>78</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>32839994</t>
+          <t>13240170</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32839994</t>
+          <t>https://m.place.naver.com/place/13240170</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1026,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>다시봄날의원 가정청라점</t>
+          <t>닥터에버스의원 청라</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>springdayclinic12@naver.com</t>
+          <t>drevers777@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-710-7525</t>
+          <t>0507-1411-8830</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 7 4층</t>
+          <t>인천광역시 서구 가정로 451 벨라미센텀시티 10층 1036호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://igc.springdayclinic.com/</t>
+          <t>https://evers7.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,7 +1058,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1095,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>282</v>
+        <v>1303</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>1305</v>
       </c>
       <c r="R7" t="n">
-        <v>294</v>
+        <v>2608</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1545423432</t>
+          <t>1008759002</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1545423432</t>
+          <t>https://m.place.naver.com/place/1008759002</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1132,25 +1120,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>연세뉴피부과의원</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>더예쁨의원</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>artificial6244@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>032-562-0712</t>
+          <t>0507-1314-6110</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 4층 405호</t>
+          <t>인천광역시 서구 중봉대로 602 청라여성병원 1층 101호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://ysnewderma.co.kr</t>
+          <t>http://theyeppeum.co.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,7 +1168,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>491</v>
+        <v>391</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>271</v>
       </c>
       <c r="R8" t="n">
-        <v>503</v>
+        <v>662</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1657698874</t>
+          <t>1315061387</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657698874</t>
+          <t>https://m.place.naver.com/place/1315061387</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1222,35 +1214,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>미라클비뇨기과의원</t>
+          <t>연세뉴피부과의원</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>032-572-8275</t>
+          <t>032-562-0712</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 363 3층 미라클</t>
+          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 4층 405호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://ysnewderma.co.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1271,17 +1263,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R9" t="n">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1282,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13137484</t>
+          <t>1657698874</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13137484</t>
+          <t>https://m.place.naver.com/place/1657698874</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1312,34 +1304,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>로지의원</t>
+          <t>데일리의원</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>srh0606@naver.com</t>
+          <t>daily_clinic@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>032-569-6515</t>
+          <t>032-567-5430</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 90 한일골드타워 201호</t>
+          <t>인천광역시 서구 솔빛로 20 도영프라자 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.rosyclinic.co.kr/</t>
+          <t>https://dailyclinic.qshop.ai/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1349,7 +1341,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1360,22 +1352,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>613</v>
+        <v>364</v>
       </c>
       <c r="Q10" t="n">
-        <v>501</v>
+        <v>112</v>
       </c>
       <c r="R10" t="n">
-        <v>1114</v>
+        <v>476</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1376,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1915321940</t>
+          <t>1443622999</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1915321940</t>
+          <t>https://m.place.naver.com/place/1443622999</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1406,29 +1398,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>더예쁨의원</t>
+          <t>킵슨의원</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>artificial6244@naver.com</t>
+          <t>keepsonmedical@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1314-6110</t>
+          <t>032-567-5337</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 602 청라여성병원 1층 101호</t>
+          <t>인천광역시 서구 청라루비로 93 루비타워 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://theyeppeum.co.kr</t>
+          <t>http://keepsonclinic.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1438,12 +1430,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1459,17 +1451,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>390</v>
+        <v>444</v>
       </c>
       <c r="Q11" t="n">
-        <v>270</v>
+        <v>98</v>
       </c>
       <c r="R11" t="n">
-        <v>660</v>
+        <v>542</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1470,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1315061387</t>
+          <t>813673396</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315061387</t>
+          <t>https://m.place.naver.com/place/813673396</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1500,34 +1492,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>닥터에버스의원 청라</t>
+          <t>이너스피부과의원</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>drevers777@naver.com</t>
+          <t>tavel-makers@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1411-8830</t>
+          <t>032-262-1777</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미센텀시티 10층 1036호</t>
+          <t>인천광역시 서구 서곶로 281 자혜빌딩 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://evers7.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1537,7 +1529,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1548,22 +1540,22 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1300</v>
+        <v>361</v>
       </c>
       <c r="Q12" t="n">
-        <v>1301</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2601</v>
+        <v>361</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1564,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1008759002</t>
+          <t>36428624</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008759002</t>
+          <t>https://m.place.naver.com/place/36428624</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1594,29 +1586,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>미엘피부과의원</t>
+          <t>미라클비뇨기과의원</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mielskin@naver.com</t>
+          <t>djsslsnstjq@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>032-572-7111</t>
+          <t>032-572-8275</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 375 403, 404호 금강아미움</t>
+          <t>인천광역시 서구 가정로 363 3층 미라클</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://ic.mielskin.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1626,7 +1618,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1651,13 +1643,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1518</v>
+        <v>484</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1521</v>
+        <v>485</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,17 +1658,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1405806250</t>
+          <t>13137484</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1405806250</t>
+          <t>https://m.place.naver.com/place/13137484</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1688,29 +1680,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>파크뷰의원 청라점</t>
+          <t>다시봄날의원 가정청라점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>parkview3300@naver.com</t>
+          <t>springdayclinic12@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>032-565-3300</t>
+          <t>032-710-7525</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 65 라임타워 파크뷰의원</t>
+          <t>인천광역시 서구 염곡로464번길 7 4층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://parkviewcl.com/</t>
+          <t>https://igc.springdayclinic.com/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1745,13 +1737,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1051</v>
+        <v>283</v>
       </c>
       <c r="Q14" t="n">
-        <v>2417</v>
+        <v>12</v>
       </c>
       <c r="R14" t="n">
-        <v>3468</v>
+        <v>295</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,17 +1752,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>34716369</t>
+          <t>1545423432</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34716369</t>
+          <t>https://m.place.naver.com/place/1545423432</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1782,25 +1774,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>서울더본피부과의원</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>더율피부과의원</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>theyulderma@naver.com</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>032-710-0075</t>
+          <t>032-225-2223</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 9-4</t>
+          <t>인천광역시 서구 중봉대로 588 406호, 407호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://seoulderborn.com</t>
+          <t>http://the-yul.co.kr/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1810,7 +1806,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1826,22 +1822,22 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>824</v>
+        <v>401</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="R15" t="n">
-        <v>833</v>
+        <v>602</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1846,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1062309841</t>
+          <t>1246412735</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1062309841</t>
+          <t>https://m.place.naver.com/place/1246412735</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1872,29 +1868,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>데일리의원</t>
+          <t>로지의원</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>daily_clinic@naver.com</t>
+          <t>srh0606@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>032-567-5430</t>
+          <t>032-569-6515</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 서구 솔빛로 20 도영프라자 2층</t>
+          <t>인천광역시 서구 봉오재3로 90 한일골드타워 201호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://dailyclinic.qshop.ai/</t>
+          <t>http://www.rosyclinic.co.kr/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1904,7 +1900,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1920,7 +1916,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1929,13 +1925,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>363</v>
+        <v>613</v>
       </c>
       <c r="Q16" t="n">
-        <v>112</v>
+        <v>506</v>
       </c>
       <c r="R16" t="n">
-        <v>475</v>
+        <v>1119</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1940,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1443622999</t>
+          <t>1915321940</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1443622999</t>
+          <t>https://m.place.naver.com/place/1915321940</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1966,33 +1962,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>킵슨의원</t>
+          <t>휴먼피부과의원 청라점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>keepsonmedical@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>jhjang@carecrm.co.kr</t>
-        </is>
-      </c>
+          <t>human___ch@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>032-567-5337</t>
+          <t>032-283-3335</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 93 루비타워 3층</t>
+          <t>인천광역시 서구 중봉대로 594 청라비전프라자 4층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/332287/items/3362791</t>
+          <t>http://www.humanic.co.kr</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2002,12 +1994,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2018,7 +2010,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2027,13 +2019,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>444</v>
+        <v>2929</v>
       </c>
       <c r="Q17" t="n">
-        <v>98</v>
+        <v>1103</v>
       </c>
       <c r="R17" t="n">
-        <v>542</v>
+        <v>4032</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,17 +2034,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>813673396</t>
+          <t>1835204658</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/813673396</t>
+          <t>https://m.place.naver.com/place/1835204658</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2064,39 +2056,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>더율피부과의원</t>
+          <t>현대아이비의원</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>theyulderma@naver.com</t>
+          <t>hdib0754@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>032-225-2223</t>
+          <t>0507-1405-0754</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 588 406호, 407호</t>
+          <t>인천광역시 서구 탁옥로 45 3층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://the-yul.co.kr/</t>
+          <t>http://www.ibclinic.co.kr/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2112,7 +2104,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2121,13 +2113,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="Q18" t="n">
-        <v>200</v>
+        <v>74</v>
       </c>
       <c r="R18" t="n">
-        <v>598</v>
+        <v>459</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,17 +2128,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1246412735</t>
+          <t>32839994</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1246412735</t>
+          <t>https://m.place.naver.com/place/32839994</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2158,29 +2150,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>휴먼피부과의원 청라점</t>
+          <t>청라브이의원</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>human___ch@naver.com</t>
+          <t>cnvclinic@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>032-283-3335</t>
+          <t>032-567-8258</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 594 청라비전프라자 4층</t>
+          <t>인천광역시 서구 청라커낼로260번길 7-11 퍼스트타워 2층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://www.humanic.co.kr</t>
+          <t>https://tinyurl.com/mr4enztn</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2190,7 +2182,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2215,13 +2207,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2926</v>
+        <v>916</v>
       </c>
       <c r="Q19" t="n">
-        <v>1098</v>
+        <v>564</v>
       </c>
       <c r="R19" t="n">
-        <v>4024</v>
+        <v>1480</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,17 +2222,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1835204658</t>
+          <t>1958745925</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835204658</t>
+          <t>https://m.place.naver.com/place/1958745925</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2252,29 +2244,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>청라브이의원</t>
+          <t>파크뷰의원 청라점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cnvclinic@naver.com</t>
+          <t>parkview3300@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>032-567-8258</t>
+          <t>032-565-3300</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 7-11 퍼스트타워 2층</t>
+          <t>인천광역시 서구 청라라임로 65 라임타워 파크뷰의원</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/mr4enztn</t>
+          <t>http://parkviewcl.com/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2289,7 +2281,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2309,13 +2301,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>917</v>
+        <v>1051</v>
       </c>
       <c r="Q20" t="n">
-        <v>568</v>
+        <v>2425</v>
       </c>
       <c r="R20" t="n">
-        <v>1485</v>
+        <v>3476</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,17 +2316,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1958745925</t>
+          <t>34716369</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958745925</t>
+          <t>https://m.place.naver.com/place/34716369</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2420,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2443,11 +2435,7 @@
           <t>밸런스마케팅</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>dailyn012@naver.com</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>bmg9449@gmail.com</t>
@@ -2526,7 +2514,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2608,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2632,29 +2620,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>청라건강한내과의원</t>
+          <t>우리베스트내과의원</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kuku337@naver.com</t>
+          <t>wooribesthealth@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>032-567-8009</t>
+          <t>032-715-6308</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 5층</t>
+          <t>인천광역시 서구 염곡로464번길 15 4층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://www.healthyclinic.kr/</t>
+          <t>http://wooribestmed.co.kr/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2685,17 +2673,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>431</v>
+        <v>1964</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>212</v>
       </c>
       <c r="R24" t="n">
-        <v>432</v>
+        <v>2176</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2704,17 +2692,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>32349771</t>
+          <t>1134694701</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32349771</t>
+          <t>https://m.place.naver.com/place/1134694701</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2726,29 +2714,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>우리베스트내과의원</t>
+          <t>청라나눔내과의원</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>wooribesthealth@naver.com</t>
+          <t>gawai31@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>032-715-6308</t>
+          <t>0507-1404-0750</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 15 4층</t>
+          <t>인천광역시 서구 청라한내로 90 MK뷰 빌딩 5층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://wooribestmed.co.kr/</t>
+          <t>http://www.nanum-clinic.com</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2758,12 +2746,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2774,7 +2762,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2783,13 +2771,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1964</v>
+        <v>918</v>
       </c>
       <c r="Q25" t="n">
-        <v>212</v>
+        <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>2176</v>
+        <v>926</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2798,17 +2786,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1134694701</t>
+          <t>37629322</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134694701</t>
+          <t>https://m.place.naver.com/place/37629322</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2811,11 @@
           <t>청라바른내과의원</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>chloemamaa@naver.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
@@ -2898,7 +2890,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2910,34 +2902,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>서울삼성의원</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>comwel2009@naver.com</t>
-        </is>
-      </c>
+          <t>청라건강한내과의원</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>032-564-9970</t>
+          <t>032-567-8009</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 587 지하2층</t>
+          <t>인천광역시 서구 청라라임로 71 5층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.healthyclinic.kr/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2967,13 +2955,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>613</v>
+        <v>431</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>627</v>
+        <v>432</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2982,17 +2970,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>36477012</t>
+          <t>32349771</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36477012</t>
+          <t>https://m.place.naver.com/place/32349771</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3004,29 +2992,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>다정한내과의원</t>
+          <t>서울삼성의원</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dajunghanim22@naver.com</t>
+          <t>comwel2009@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1349-7511</t>
+          <t>032-564-9970</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 81 2층</t>
+          <t>인천광역시 서구 중봉대로 587 지하2층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dajunghanim22</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3036,12 +3024,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3061,13 +3049,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>641</v>
+        <v>613</v>
       </c>
       <c r="Q28" t="n">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="R28" t="n">
-        <v>841</v>
+        <v>627</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3076,17 +3064,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>38270484</t>
+          <t>36477012</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38270484</t>
+          <t>https://m.place.naver.com/place/36477012</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3098,29 +3086,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>청라나눔내과의원</t>
+          <t>다정한내과의원</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gawai31@naver.com</t>
+          <t>dajunghanim22@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1404-0750</t>
+          <t>0507-1349-7511</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 90 MK뷰 빌딩 5층</t>
+          <t>인천광역시 서구 청라루비로 81 2층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://www.nanum-clinic.com</t>
+          <t>https://blog.naver.com/dajunghanim22</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3135,7 +3123,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3151,17 +3139,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>918</v>
+        <v>641</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="R29" t="n">
-        <v>926</v>
+        <v>842</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3170,17 +3158,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>37629322</t>
+          <t>38270484</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37629322</t>
+          <t>https://m.place.naver.com/place/38270484</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3266,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3281,11 @@
           <t>미스토리의원</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>cherry3559@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -3368,7 +3360,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3440,10 +3432,10 @@
         <v>258</v>
       </c>
       <c r="Q32" t="n">
-        <v>413</v>
+        <v>344</v>
       </c>
       <c r="R32" t="n">
-        <v>671</v>
+        <v>602</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3462,7 +3454,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3556,41 +3548,41 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>병원부속시설</t>
+          <t>병원,의원</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>소통부부한의원 청라 피부미용클리닉</t>
+          <t>청라세란메디컬의원</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>et_news@naver.com</t>
+          <t>hadw722@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>032-710-1473</t>
+          <t>032-203-3300</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 65 라임타워 7층</t>
+          <t>인천광역시 서구 중봉대로 490 126~127호 (청라동)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sotongbeauty</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3600,7 +3592,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3621,17 +3613,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>428</v>
+        <v>6</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3640,51 +3632,51 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2046680647</t>
+          <t>1312583637</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2046680647</t>
+          <t>https://m.place.naver.com/place/1312583637</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>비뇨의학과</t>
+          <t>병원부속시설</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>루원삼성비뇨의학과의원</t>
+          <t>소통부부한의원 청라 피부미용클리닉</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>lu1samsung@naver.com</t>
+          <t>et_news@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>032-565-0728</t>
+          <t>032-710-1473</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 90</t>
+          <t>인천광역시 서구 청라라임로 65 라임타워 7층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lu1samsung</t>
+          <t>https://www.instagram.com/sotongbeauty</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3699,7 +3691,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3715,17 +3707,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>117</v>
+        <v>478</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>119</v>
+        <v>478</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3734,17 +3726,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1166037095</t>
+          <t>2046680647</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166037095</t>
+          <t>https://m.place.naver.com/place/2046680647</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3756,29 +3748,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>엘림비뇨기과의원</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>binterest@naver.com</t>
-        </is>
-      </c>
+          <t>라임비뇨의학과의원 청라점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>032-577-7533</t>
+          <t>0507-1438-5388</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 308 석남프라자</t>
+          <t>인천광역시 서구 중봉대로 594 504~505호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>http://www.elimuro.com/</t>
+          <t>http://limeurology10.co.kr</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3788,7 +3776,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3804,7 +3792,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3813,13 +3801,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="R36" t="n">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3828,17 +3816,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>11607252</t>
+          <t>35593344</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11607252</t>
+          <t>https://m.place.naver.com/place/35593344</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3850,44 +3838,44 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>라임비뇨의학과의원 청라점</t>
+          <t>루원삼성비뇨의학과의원</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>gentleman_repair@naver.com</t>
+          <t>lu1samsung@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1438-5388</t>
+          <t>032-565-0728</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 594 504~505호</t>
+          <t>인천광역시 서구 봉오재3로 90</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://limeurology10.co.kr</t>
+          <t>https://blog.naver.com/lu1samsung</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3898,7 +3886,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3907,13 +3895,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="Q37" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>209</v>
+        <v>119</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3922,57 +3910,61 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>35593344</t>
+          <t>1166037095</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35593344</t>
+          <t>https://m.place.naver.com/place/1166037095</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>성형외과</t>
+          <t>비뇨의학과</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>명메디칼스킨남성의원</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>엘림비뇨기과의원</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>binterest@naver.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>032-561-7564</t>
+          <t>032-577-7533</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 364-1 창대빌딩</t>
+          <t>인천광역시 서구 가정로 308 석남프라자</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.elimuro.com/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3997,13 +3989,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>55</v>
+        <v>173</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4012,51 +4004,51 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>19513442</t>
+          <t>11607252</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19513442</t>
+          <t>https://m.place.naver.com/place/11607252</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>소아청소년과</t>
+          <t>성형외과</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아이비소아청소년과의원</t>
+          <t>명메디칼스킨남성의원</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>happysofa_net@naver.com</t>
+          <t>flalswnwn@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>032-473-7575</t>
+          <t>032-561-7564</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 51 에일린의 뜰 208호</t>
+          <t>인천광역시 서구 가정로 364-1 창대빌딩</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://www.ivycare.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4066,7 +4058,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4091,13 +4083,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>466</v>
+        <v>55</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>491</v>
+        <v>56</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4106,17 +4098,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>20780682</t>
+          <t>19513442</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20780682</t>
+          <t>https://m.place.naver.com/place/19513442</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4128,44 +4120,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>청라미소소아청소년과의원</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>misoped_clinic@naver.com</t>
-        </is>
-      </c>
+          <t>사랑소아청소년과의원</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>032-563-7227</t>
+          <t>0507-1366-8277</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 10 505호</t>
+          <t>인천광역시 서구 새오개로111번안길 31 도모빌딩2층 사랑소아청소년과</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/misoped_clinic</t>
+          <t>https://short.ddocdoc.com/2b2vhj</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4185,13 +4173,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4200,17 +4188,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1965538592</t>
+          <t>1324399229</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965538592</t>
+          <t>https://m.place.naver.com/place/1324399229</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4222,25 +4210,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>아이사랑소아청소년과의원</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>365별소아청소년과의원</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>dygks0823@naver.com</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>032-561-0279</t>
+          <t>032-581-9900</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 40 202호</t>
+          <t>인천광역시 서구 가정로 375 금강아미움 3층 304호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://iloveped.medisay.co.kr</t>
+          <t>http://365star.ilikedoc.kr/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4250,7 +4242,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4275,13 +4267,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>171</v>
+        <v>1100</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="R41" t="n">
-        <v>177</v>
+        <v>1120</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,17 +4282,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1089940606</t>
+          <t>37263561</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089940606</t>
+          <t>https://m.place.naver.com/place/37263561</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4312,34 +4304,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>청라튼튼소아청소년과의원</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>luwon365@naver.com</t>
-        </is>
-      </c>
+          <t>아이사랑소아청소년과의원</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>032-564-5955</t>
+          <t>032-561-0279</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 서구 솔빛로 24 부영프라자 201호</t>
+          <t>인천광역시 서구 봉오재3로 40 202호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://iloveped.medisay.co.kr</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4369,13 +4357,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>400</v>
+        <v>171</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R42" t="n">
-        <v>405</v>
+        <v>177</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4384,17 +4372,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>35516433</t>
+          <t>1089940606</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35516433</t>
+          <t>https://m.place.naver.com/place/1089940606</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4406,34 +4394,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>365별소아청소년과의원</t>
+          <t>청라미소소아청소년과의원</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>dygks0823@naver.com</t>
+          <t>misoped_clinic@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>032-581-9900</t>
+          <t>032-563-7227</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 375 금강아미움 3층 304호</t>
+          <t>인천광역시 서구 청라커낼로288번길 10 505호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://365star.ilikedoc.kr/</t>
+          <t>https://blog.naver.com/misoped_clinic</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4443,7 +4431,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4463,13 +4451,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1100</v>
+        <v>94</v>
       </c>
       <c r="Q43" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="R43" t="n">
-        <v>1120</v>
+        <v>103</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4478,17 +4466,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>37263561</t>
+          <t>1965538592</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37263561</t>
+          <t>https://m.place.naver.com/place/1965538592</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4500,39 +4488,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>사랑소아청소년과의원</t>
+          <t>해맑은소아청소년과의원</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>twoulike@naver.com</t>
+          <t>aidaot3@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1366-8277</t>
+          <t>032-569-7588</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 서구 새오개로111번안길 31 도모빌딩2층 사랑소아청소년과</t>
+          <t>인천광역시 서구 청라라임로 71</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://short.ddocdoc.com/2b2vhj</t>
+          <t>http://brightped.co.kr/index.asp</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4557,13 +4545,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="R44" t="n">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4572,17 +4560,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1324399229</t>
+          <t>20107762</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324399229</t>
+          <t>https://m.place.naver.com/place/20107762</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4594,29 +4582,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>해맑은소아청소년과의원</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>aidaot3@naver.com</t>
-        </is>
-      </c>
+          <t>아이비소아청소년과의원</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>032-569-7588</t>
+          <t>032-473-7575</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71</t>
+          <t>인천광역시 서구 청라라임로 51 에일린의 뜰 208호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://brightped.co.kr/index.asp</t>
+          <t>http://www.ivycare.co.kr/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4651,13 +4635,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>150</v>
+        <v>466</v>
       </c>
       <c r="Q45" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="R45" t="n">
-        <v>167</v>
+        <v>491</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4666,17 +4650,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>20107762</t>
+          <t>20780682</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20107762</t>
+          <t>https://m.place.naver.com/place/20780682</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4745,13 +4729,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="Q46" t="n">
         <v>10</v>
       </c>
       <c r="R46" t="n">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4770,7 +4754,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4782,29 +4766,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>상이비인후과</t>
+          <t>열린이비인후과의원</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>hjmi4686@naver.com</t>
+          <t>letmeshow111@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>032-572-7582</t>
+          <t>032-565-0938</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 372 2층</t>
+          <t>인천광역시 서구 봉오재3로 44 명문프라자 2층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/letmeshow111</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4814,12 +4798,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4839,13 +4823,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>313</v>
+        <v>634</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="R47" t="n">
-        <v>317</v>
+        <v>734</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4854,17 +4838,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13240086</t>
+          <t>888152498</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240086</t>
+          <t>https://m.place.naver.com/place/888152498</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4876,29 +4860,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>열린이비인후과의원</t>
+          <t>율 이비인후과 의원</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>letmeshow111@naver.com</t>
+          <t>yul_ent@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>032-565-0938</t>
+          <t>0507-1349-4606</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 44 명문프라자 2층</t>
+          <t>인천광역시 서구 청라한내로 96 3층 303, 304, 305호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/letmeshow111</t>
+          <t>https://www.yulent.net</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4908,7 +4892,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4933,13 +4917,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>633</v>
+        <v>50</v>
       </c>
       <c r="Q48" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>731</v>
+        <v>50</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4948,17 +4932,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>888152498</t>
+          <t>2061001738</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/888152498</t>
+          <t>https://m.place.naver.com/place/2061001738</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4970,44 +4954,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>율 이비인후과 의원</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>yul_ent@naver.com</t>
-        </is>
-      </c>
+          <t>열린성모이비인후과의원</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1349-4606</t>
+          <t>032-885-8275</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 96 3층 303, 304, 305호</t>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 5층 열린성모이비인후과</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.yulent.net</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5027,13 +5007,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>49</v>
+        <v>360</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>49</v>
+        <v>363</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5042,17 +5022,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2061001738</t>
+          <t>36728069</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061001738</t>
+          <t>https://m.place.naver.com/place/36728069</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5064,20 +5044,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>열린성모이비인후과의원</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>상이비인후과</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>hjmi4686@naver.com</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>032-885-8275</t>
+          <t>032-572-7582</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 진영메디피아 5층 열린성모이비인후과</t>
+          <t>인천광역시 서구 가정로 372 2층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5117,13 +5101,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>359</v>
+        <v>313</v>
       </c>
       <c r="Q50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R50" t="n">
-        <v>362</v>
+        <v>317</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5132,17 +5116,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>36728069</t>
+          <t>13240086</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36728069</t>
+          <t>https://m.place.naver.com/place/13240086</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5211,13 +5195,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="Q51" t="n">
         <v>17</v>
       </c>
       <c r="R51" t="n">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5236,7 +5220,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5248,39 +5232,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>제대로정형외과마취통증의학과의원</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>astondis@naver.com</t>
-        </is>
-      </c>
+          <t>가정성모의원</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>032-1522-7235</t>
+          <t>0507-1390-7586</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로 78 4층</t>
+          <t>인천광역시 서구 청중로 486 부일프라자 3, 4층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://www.jdrhospital.com/</t>
+          <t>http://gajeongsm.co.kr</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5305,13 +5285,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>624</v>
+        <v>330</v>
       </c>
       <c r="Q52" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="R52" t="n">
-        <v>633</v>
+        <v>400</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5320,17 +5300,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>38494766</t>
+          <t>38674023</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38494766</t>
+          <t>https://m.place.naver.com/place/38674023</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5342,29 +5322,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>진정형외과의원</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>lovehosp@naver.com</t>
-        </is>
-      </c>
+          <t>청라성모정형외과의원</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>032-566-0085</t>
+          <t>032-567-3334</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 264 403~404호</t>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아3층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.청라성모정형외과.com/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5374,7 +5350,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5399,13 +5375,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>267</v>
+        <v>1017</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="R53" t="n">
-        <v>272</v>
+        <v>1036</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5414,17 +5390,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>38667983</t>
+          <t>34053041</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38667983</t>
+          <t>https://m.place.naver.com/place/34053041</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5436,30 +5412,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>청라성모정형외과의원</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>드림재활의학과의원</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sand14287@naver.com</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>032-567-3334</t>
+          <t>0507-1405-7177</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 진영메디피아3층</t>
+          <t>인천광역시 서구 중봉대로 588</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://www.청라성모정형외과.com/</t>
+          <t>https://blog.naver.com/sand14287</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5469,7 +5449,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5489,13 +5469,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1017</v>
+        <v>239</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="R54" t="n">
-        <v>1036</v>
+        <v>280</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5504,17 +5484,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>34053041</t>
+          <t>32473115</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34053041</t>
+          <t>https://m.place.naver.com/place/32473115</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5526,35 +5506,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>가정성모의원</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>제대로정형외과마취통증의학과의원</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>astondis@naver.com</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1390-7586</t>
+          <t>032-1522-7235</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청중로 486 부일프라자 3, 4층</t>
+          <t>인천광역시 서구 크리스탈로 78 4층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://gajeongsm.co.kr</t>
+          <t>http://www.jdrhospital.com/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5579,13 +5563,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>330</v>
+        <v>624</v>
       </c>
       <c r="Q55" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="R55" t="n">
-        <v>400</v>
+        <v>633</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5594,17 +5578,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>38674023</t>
+          <t>38494766</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38674023</t>
+          <t>https://m.place.naver.com/place/38494766</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5616,29 +5600,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>드림재활의학과의원</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>sand14287@naver.com</t>
-        </is>
-      </c>
+          <t>진정형외과의원</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1405-7177</t>
+          <t>032-566-0085</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 588</t>
+          <t>인천광역시 서구 청라커낼로 264 403~404호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sand14287</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5648,12 +5628,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5673,13 +5653,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="Q56" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="R56" t="n">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5688,17 +5668,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>32473115</t>
+          <t>38667983</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32473115</t>
+          <t>https://m.place.naver.com/place/38667983</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5710,29 +5690,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>청라S한방병원</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>cnskm_@naver.com</t>
-        </is>
-      </c>
+          <t>청라좋은한방병원</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1343-8258</t>
+          <t>032-568-2005</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 9-4 6층, 8층</t>
+          <t>인천광역시 서구 청라에메랄드로 79 2층~4층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://cnskm.co.kr</t>
+          <t>http://cn-hani.co.kr/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5767,13 +5743,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>692</v>
+        <v>631</v>
       </c>
       <c r="Q57" t="n">
-        <v>3174</v>
+        <v>1125</v>
       </c>
       <c r="R57" t="n">
-        <v>3866</v>
+        <v>1756</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5782,17 +5758,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1676688118</t>
+          <t>2095160385</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1676688118</t>
+          <t>https://m.place.naver.com/place/2095160385</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5804,30 +5780,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>청라좋은한방병원</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>서인천한방병원</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>chtjdus@naver.com</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>032-568-2005</t>
+          <t>032-521-7582</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 2층~4층</t>
+          <t>인천광역시 서구 염곡로464번길 7 6층 서인천한방병원</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://cn-hani.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5837,7 +5817,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5848,7 +5828,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5857,13 +5837,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>613</v>
+        <v>207</v>
       </c>
       <c r="Q58" t="n">
-        <v>1127</v>
+        <v>874</v>
       </c>
       <c r="R58" t="n">
-        <v>1740</v>
+        <v>1081</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5872,17 +5852,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2095160385</t>
+          <t>1042604346</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095160385</t>
+          <t>https://m.place.naver.com/place/1042604346</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5894,34 +5874,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>서인천한방병원</t>
+          <t>인정한방병원</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>chtjdus@naver.com</t>
+          <t>haecare@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>032-521-7582</t>
+          <t>0507-1356-7782</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 7 6층 서인천한방병원</t>
+          <t>인천광역시 서구 청라에메랄드로 99 B동 5층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.injungmedi.com</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5931,7 +5911,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5942,7 +5922,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5951,13 +5931,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="Q59" t="n">
-        <v>871</v>
+        <v>929</v>
       </c>
       <c r="R59" t="n">
-        <v>1078</v>
+        <v>1114</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5966,17 +5946,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1042604346</t>
+          <t>1428648030</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1042604346</t>
+          <t>https://m.place.naver.com/place/1428648030</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5988,29 +5968,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>인정한방병원</t>
+          <t>청라S한방병원</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>haecare@naver.com</t>
+          <t>cnskm_@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1356-7782</t>
+          <t>0507-1343-8258</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 B동 5층</t>
+          <t>인천광역시 서구 중봉대로586번길 9-4 6층, 8층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.injungmedi.com</t>
+          <t>http://cnskm.co.kr</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6045,13 +6025,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>185</v>
+        <v>708</v>
       </c>
       <c r="Q60" t="n">
-        <v>926</v>
+        <v>3285</v>
       </c>
       <c r="R60" t="n">
-        <v>1111</v>
+        <v>3993</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6060,17 +6040,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1428648030</t>
+          <t>1676688118</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1428648030</t>
+          <t>https://m.place.naver.com/place/1676688118</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6082,29 +6062,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>경희명한의원</t>
+          <t>정본한의원</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ymungz@naver.com</t>
+          <t>sangkakim1@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1399-8123</t>
+          <t>0507-1394-8004</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 서구 푸른로 3 2층</t>
+          <t>인천광역시 서구 가정로 379 진원빌딩 4층 402호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://www.koreamedicine.co.kr</t>
+          <t>https://www.jeongbone.com</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6135,17 +6115,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>259</v>
+        <v>1093</v>
       </c>
       <c r="Q61" t="n">
-        <v>7</v>
+        <v>2808</v>
       </c>
       <c r="R61" t="n">
-        <v>266</v>
+        <v>3901</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6154,17 +6134,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>13238392</t>
+          <t>1623452423</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13238392</t>
+          <t>https://m.place.naver.com/place/1623452423</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6176,34 +6156,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>단비한의원</t>
+          <t>인영한의원</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>danbimkv@naver.com</t>
+          <t>inyounggg_@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1481-1081</t>
+          <t>0507-1442-4848</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 90 엠케이뷰 6층 단비한의원</t>
+          <t>인천광역시 서구 중봉대로 588 7층 709호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/danbImkv</t>
+          <t>https://inyounghani.com/</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6229,17 +6209,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="Q62" t="n">
-        <v>50</v>
+        <v>1435</v>
       </c>
       <c r="R62" t="n">
-        <v>270</v>
+        <v>1640</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6248,17 +6228,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1068245349</t>
+          <t>1527071512</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1068245349</t>
+          <t>https://m.place.naver.com/place/1527071512</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6270,44 +6250,44 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>뜰한의원</t>
+          <t>소통부부한의원 청라</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>gardenhani@naver.com</t>
+          <t>sotongbbcn@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1473-1472</t>
+          <t>0507-1498-3420</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 10 4층 406호</t>
+          <t>인천광역시 서구 청라라임로 65 4층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gardenhani</t>
+          <t>http://www.sotongbooboo.co.kr/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6318,22 +6298,22 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>222</v>
+        <v>1655</v>
       </c>
       <c r="Q63" t="n">
-        <v>103</v>
+        <v>3536</v>
       </c>
       <c r="R63" t="n">
-        <v>325</v>
+        <v>5191</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6342,17 +6322,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1152812855</t>
+          <t>35734767</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1152812855</t>
+          <t>https://m.place.naver.com/place/35734767</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6364,34 +6344,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>일등한의원 인천가정</t>
+          <t>뜰한의원</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ildungno1@naver.com</t>
+          <t>gardenhani@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>032-710-3969</t>
+          <t>0507-1473-1472</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 378 2층</t>
+          <t>인천광역시 서구 청라커낼로288번길 10 4층 406호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rNPHb</t>
+          <t>https://blog.naver.com/gardenhani</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6401,7 +6381,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6412,7 +6392,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6421,13 +6401,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2002</v>
+        <v>223</v>
       </c>
       <c r="Q64" t="n">
-        <v>1253</v>
+        <v>103</v>
       </c>
       <c r="R64" t="n">
-        <v>3255</v>
+        <v>326</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6436,17 +6416,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1608876929</t>
+          <t>1152812855</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1608876929</t>
+          <t>https://m.place.naver.com/place/1152812855</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6518,10 +6498,10 @@
         <v>498</v>
       </c>
       <c r="Q65" t="n">
-        <v>2268</v>
+        <v>2290</v>
       </c>
       <c r="R65" t="n">
-        <v>2766</v>
+        <v>2788</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6540,7 +6520,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6552,44 +6532,44 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>청라맑은샘한의원 청라</t>
+          <t>경희명한의원</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>mfxignhacq955@naver.com</t>
+          <t>ymungz@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1364-1240</t>
+          <t>0507-1399-8123</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 93 루비타워 205호</t>
+          <t>인천광역시 서구 푸른로 3 2층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://youtu.be/bwEb-MbSvTg?si=qywW0LXKoCEcRhN3</t>
+          <t>http://www.koreamedicine.co.kr</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6609,13 +6589,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>953</v>
+        <v>259</v>
       </c>
       <c r="Q66" t="n">
-        <v>1034</v>
+        <v>7</v>
       </c>
       <c r="R66" t="n">
-        <v>1987</v>
+        <v>266</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6624,17 +6604,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1161608478</t>
+          <t>13238392</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161608478</t>
+          <t>https://m.place.naver.com/place/13238392</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6646,34 +6626,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>이주한의원</t>
+          <t>일등한의원 인천가정</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>leejookmc@naver.com</t>
+          <t>ildungno1@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>032-719-7565</t>
+          <t>032-710-3969</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 청라린스트라우스 A동 206호</t>
+          <t>인천광역시 서구 가정로 378 2층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leejookmc</t>
+          <t>http://pf.kakao.com/_rNPHb</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6683,7 +6663,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6694,7 +6674,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6703,13 +6683,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>74</v>
+        <v>2033</v>
       </c>
       <c r="Q67" t="n">
-        <v>59</v>
+        <v>1252</v>
       </c>
       <c r="R67" t="n">
-        <v>133</v>
+        <v>3285</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6718,17 +6698,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1421602346</t>
+          <t>1608876929</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421602346</t>
+          <t>https://m.place.naver.com/place/1608876929</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6740,34 +6720,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>루원365한의원 인천가정역점</t>
+          <t>단비한의원</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>leesak0310@naver.com</t>
+          <t>danbimkv@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1323-4975</t>
+          <t>0507-1481-1081</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 15 쓰리엠타워 3층</t>
+          <t>인천광역시 서구 청라한내로 90 엠케이뷰 6층 단비한의원</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://www.ru1.kr</t>
+          <t>https://www.instagram.com/danbImkv</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6788,22 +6768,22 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>863</v>
+        <v>220</v>
       </c>
       <c r="Q68" t="n">
-        <v>601</v>
+        <v>50</v>
       </c>
       <c r="R68" t="n">
-        <v>1464</v>
+        <v>270</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6812,17 +6792,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1264346896</t>
+          <t>1068245349</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264346896</t>
+          <t>https://m.place.naver.com/place/1068245349</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6834,44 +6814,44 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>청라함소아한의원</t>
+          <t>루원365한의원 인천가정역점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>cn_hamsoa@naver.com</t>
+          <t>leesak0310@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1497-1331</t>
+          <t>0507-1323-4975</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 94 3층</t>
+          <t>인천광역시 서구 염곡로464번길 15 쓰리엠타워 3층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cn_hamsoa</t>
+          <t>http://www.ru1.kr</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6882,22 +6862,22 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>212</v>
+        <v>871</v>
       </c>
       <c r="Q69" t="n">
-        <v>20</v>
+        <v>608</v>
       </c>
       <c r="R69" t="n">
-        <v>232</v>
+        <v>1479</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6906,17 +6886,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>30811670</t>
+          <t>1264346896</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30811670</t>
+          <t>https://m.place.naver.com/place/1264346896</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6985,13 +6965,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q70" t="n">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="R70" t="n">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7010,7 +6990,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7022,34 +7002,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>인영한의원</t>
+          <t>신농씨한의원</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>inyounggg_@naver.com</t>
+          <t>shinnong71@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1442-4848</t>
+          <t>0507-1330-1075</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 588 7층 709호</t>
+          <t>인천광역시 서구 청라라임로 71 505호 신농씨한의원</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://inyounghani.com/</t>
+          <t>https://blog.naver.com/shinnong71</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7059,7 +7039,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7079,13 +7059,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>205</v>
+        <v>1161</v>
       </c>
       <c r="Q71" t="n">
-        <v>1415</v>
+        <v>235</v>
       </c>
       <c r="R71" t="n">
-        <v>1620</v>
+        <v>1396</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7094,17 +7074,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1527071512</t>
+          <t>21039223</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527071512</t>
+          <t>https://m.place.naver.com/place/21039223</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7173,13 +7153,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="Q72" t="n">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="R72" t="n">
-        <v>603</v>
+        <v>618</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7198,7 +7178,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7210,39 +7190,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>정본한의원</t>
+          <t>청라 리아한의원</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>sangkakim1@naver.com</t>
+          <t>wlsdudtn04@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1394-8004</t>
+          <t>0507-1372-4975</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 379 진원빌딩 4층 402호</t>
+          <t>인천광역시 서구 중봉대로612번길 10-17 청라타워돔 3층 리아한의원</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.jeongbone.com</t>
+          <t>https://blog.naver.com/wlsdudtn04</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7263,17 +7243,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1093</v>
+        <v>433</v>
       </c>
       <c r="Q73" t="n">
-        <v>2753</v>
+        <v>2167</v>
       </c>
       <c r="R73" t="n">
-        <v>3846</v>
+        <v>2600</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7282,17 +7262,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1623452423</t>
+          <t>37485905</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623452423</t>
+          <t>https://m.place.naver.com/place/37485905</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7304,44 +7284,44 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>소통부부한의원 청라</t>
+          <t>이주한의원</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sotongbbcn@naver.com</t>
+          <t>leejookmc@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1498-3420</t>
+          <t>032-719-7565</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 65 4층</t>
+          <t>인천광역시 서구 청라라임로 85 청라린스트라우스 A동 206호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://www.sotongbooboo.co.kr/</t>
+          <t>https://blog.naver.com/leejookmc</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7352,22 +7332,22 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1644</v>
+        <v>74</v>
       </c>
       <c r="Q74" t="n">
-        <v>3502</v>
+        <v>62</v>
       </c>
       <c r="R74" t="n">
-        <v>5146</v>
+        <v>136</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7376,17 +7356,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>35734767</t>
+          <t>1421602346</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35734767</t>
+          <t>https://m.place.naver.com/place/1421602346</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7398,29 +7378,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>청라 리아한의원</t>
+          <t>청라함소아한의원</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>wlsdudtn04@naver.com</t>
+          <t>cn_hamsoa@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1372-4975</t>
+          <t>0507-1497-1331</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-17 청라타워돔 3층 리아한의원</t>
+          <t>인천광역시 서구 청라에메랄드로 94 3층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wlsdudtn04</t>
+          <t>https://blog.naver.com/cn_hamsoa</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7451,17 +7431,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>430</v>
+        <v>212</v>
       </c>
       <c r="Q75" t="n">
-        <v>2120</v>
+        <v>20</v>
       </c>
       <c r="R75" t="n">
-        <v>2550</v>
+        <v>232</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7470,17 +7450,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>37485905</t>
+          <t>30811670</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37485905</t>
+          <t>https://m.place.naver.com/place/30811670</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7492,34 +7472,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>신농씨한의원</t>
+          <t>청라맑은샘한의원 청라</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>shinnong71@naver.com</t>
+          <t>mfxignhacq955@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1330-1075</t>
+          <t>0507-1364-1240</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 505호 신농씨한의원</t>
+          <t>인천광역시 서구 청라루비로 93 루비타워 205호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/shinnong71</t>
+          <t>https://youtu.be/bwEb-MbSvTg?si=qywW0LXKoCEcRhN3</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7529,7 +7509,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7549,13 +7529,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1158</v>
+        <v>954</v>
       </c>
       <c r="Q76" t="n">
-        <v>235</v>
+        <v>1035</v>
       </c>
       <c r="R76" t="n">
-        <v>1393</v>
+        <v>1989</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7564,17 +7544,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>21039223</t>
+          <t>1161608478</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21039223</t>
+          <t>https://m.place.naver.com/place/1161608478</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
